--- a/02_DIA_inicio_2026_analisis_assets/rbd_9726_liceo-teniente-francisco-mery-aguirre_nt2_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9726_liceo-teniente-francisco-mery-aguirre_nt2_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{930EF97A-EAB1-41B6-B363-4B4865481594}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37649B4B-989C-4A03-A0E7-4E6C694B8A8C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{731A7FD8-2B25-4F1A-9600-E370CC5B9256}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5D0FE0D-E4DA-45C4-81FD-A6F8C991BD13}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C4F4CC2-D206-4623-88BD-60D466FA2556}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{903D8C5B-1182-4CE2-91A9-CD567B5C2513}"/>
 </file>